--- a/Employee_Reports_wi52/Sajith Dulanjana Kumara Rathnayaka Mudiyanselage Q0626.xlsx
+++ b/Employee_Reports_wi52/Sajith Dulanjana Kumara Rathnayaka Mudiyanselage Q0626.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1145,11 +1145,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1194,11 +1194,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1244,11 +1244,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1404,6 +1404,43 @@
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>727</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1667,7 +1704,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1762,7 +1799,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1791,7 +1828,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1820,7 +1857,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1849,7 +1886,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1878,7 +1915,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1944,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1973,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1965,7 +2002,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1994,7 +2031,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2060,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2052,7 +2089,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7943</v>
+        <v>7935</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2081,7 +2118,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7943</v>
+        <v>7935</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2110,7 +2147,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7943</v>
+        <v>7935</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2139,7 +2176,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7943</v>
+        <v>7935</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2205,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2197,7 +2234,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2263,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2255,7 +2292,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
